--- a/マッピング表(倉庫名⇔保管場所名).xlsx
+++ b/マッピング表(倉庫名⇔保管場所名).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD03154-D71D-4960-8DAB-9D36D7837445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE35A611-3289-45CF-836B-65BACC1F727F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4872" yWindow="864" windowWidth="17184" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="変換表" sheetId="2" r:id="rId1"/>
@@ -104,9 +104,6 @@
     <t>高松ＷＨ</t>
   </si>
   <si>
-    <t>山形</t>
-  </si>
-  <si>
     <t>保管場所名</t>
   </si>
   <si>
@@ -196,6 +193,9 @@
   </si>
   <si>
     <t>株式会社ＰＦＵ／岡山（都窪郡）</t>
+  </si>
+  <si>
+    <t>東日本・山形倉庫</t>
   </si>
 </sst>
 </file>
@@ -605,15 +605,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -621,15 +621,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -637,7 +637,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
@@ -645,7 +645,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
@@ -653,7 +653,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>5</v>
@@ -661,7 +661,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>7</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>6</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>20</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>4</v>
@@ -701,7 +701,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>18</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>1</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>3</v>
@@ -725,7 +725,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>12</v>
@@ -733,7 +733,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>11</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>0</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
@@ -757,7 +757,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
@@ -765,7 +765,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>19</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>17</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>8</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>21</v>
